--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487101_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487101_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4749</v>
+        <v>2.575</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1254</v>
+        <v>4.2256</v>
       </c>
       <c r="F2" t="n">
         <v>-1.6505</v>
@@ -610,10 +610,10 @@
         <v>1.3511</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0304</v>
+        <v>0.0697</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0727</v>
+        <v>0.1729</v>
       </c>
       <c r="U2" t="n">
         <v>-0.1031</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7299</v>
+        <v>0.9103</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1665</v>
+        <v>2.2667</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4367</v>
+        <v>-1.3564</v>
       </c>
       <c r="G3" t="n">
         <v>-2.4064</v>
@@ -688,13 +688,13 @@
         <v>1.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0218</v>
+        <v>0.1586</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1057</v>
+        <v>-0.0056</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0839</v>
+        <v>0.1642</v>
       </c>
       <c r="V3" t="n">
         <v>1.228</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ALDA IRAOLA</t>
+          <t>E. ERRASTI URANGA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1742</v>
+        <v>0.5573</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7956</v>
+        <v>1.5207</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6214</v>
+        <v>-0.9634</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.4969</v>
+        <v>-1.4837</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7823</v>
+        <v>-2.2148</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.2792</v>
+        <v>0.7311</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3527</v>
+        <v>0.5653</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5251</v>
+        <v>-0.1915</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1724</v>
+        <v>0.7569</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8496</v>
+        <v>-2.049</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7428</v>
+        <v>-2.0233</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1067</v>
+        <v>-0.0257</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9301</v>
+        <v>1.3511</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9301</v>
+        <v>1.3511</v>
       </c>
       <c r="S4" t="n">
-        <v>0.355</v>
+        <v>-0.538</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4429</v>
+        <v>-0.2726</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.2654</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.614</v>
+        <v>1.228</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. ERRASTI URANGA</t>
+          <t>A. ALDA IRAOLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1903</v>
+        <v>-0.2333</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9605</v>
+        <v>1.2542</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1507</v>
+        <v>-1.4876</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4837</v>
+        <v>-1.4969</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.2148</v>
+        <v>0.7823</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7311</v>
+        <v>-2.2792</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5653</v>
+        <v>1.3527</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1915</v>
+        <v>2.5251</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7569</v>
+        <v>-1.1724</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.049</v>
+        <v>-2.8496</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0233</v>
+        <v>-1.7428</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0257</v>
+        <v>-1.1067</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3511</v>
+        <v>1.9301</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3511</v>
+        <v>1.9301</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2856</v>
+        <v>-0.0525</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8328</v>
+        <v>-0.0985</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4528</v>
+        <v>0.0459</v>
       </c>
       <c r="V5" t="n">
-        <v>1.228</v>
+        <v>-0.614</v>
       </c>
       <c r="W5" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. URTXULUTEGI NAVARRI</t>
+          <t>U. PEREZ SANZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7030999999999999</v>
+        <v>-0.5394</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0581</v>
+        <v>1.9603</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7611</v>
+        <v>-2.4997</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.5718</v>
+        <v>0.7679</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7057</v>
+        <v>1.1685</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8661</v>
+        <v>-0.4006</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6226</v>
+        <v>5.5533</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0364</v>
+        <v>4.3002</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5862000000000001</v>
+        <v>1.2531</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9493</v>
+        <v>-4.7854</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6694</v>
+        <v>-3.1317</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2799</v>
+        <v>-1.6537</v>
       </c>
       <c r="P6" t="n">
-        <v>0.386</v>
+        <v>-0.386</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3511</v>
+        <v>2.5091</v>
       </c>
       <c r="S6" t="n">
-        <v>2.139</v>
+        <v>-0.7985</v>
       </c>
       <c r="T6" t="n">
-        <v>2.016</v>
+        <v>-0.3698</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1229</v>
+        <v>-0.4287</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6562</v>
+        <v>-0.1228</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3704</v>
+        <v>-0.3281</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2859</v>
+        <v>0.2053</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0346</v>
+        <v>-1.3152</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1352</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1698</v>
+        <v>-1.2501</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9231</v>
@@ -1000,13 +1000,13 @@
         <v>0.193</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3325</v>
+        <v>0.0519</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4891</v>
+        <v>0.2889</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1567</v>
+        <v>-0.237</v>
       </c>
       <c r="V7" t="n">
         <v>0.3281</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>J. ELOSEGUI OLANO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3008</v>
+        <v>-1.8615</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5987</v>
+        <v>-0.8423</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-1.0192</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7323</v>
+        <v>-1.1265</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.457</v>
+        <v>-0.4461</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7247</v>
+        <v>-0.6805</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1978</v>
+        <v>0.0414</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2267</v>
+        <v>0.0414</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4245</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.93</v>
+        <v>-1.1679</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.2303</v>
+        <v>-0.4875</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6998</v>
+        <v>-0.6805</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.772</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.965</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.193</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.9301</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.1231</v>
-      </c>
       <c r="S8" t="n">
-        <v>1.0754</v>
+        <v>0.037</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5619</v>
+        <v>0.0813</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5135999999999999</v>
+        <v>-0.0443</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1631</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4087</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>U. PEREZ SANZ</t>
+          <t>J. URTXULUTEGI NAVARRI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6478</v>
+        <v>-2.112</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1998</v>
+        <v>-1.2438</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8477</v>
+        <v>-0.8682</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7679</v>
+        <v>-2.5718</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1685</v>
+        <v>-1.7057</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4006</v>
+        <v>-0.8661</v>
       </c>
       <c r="J9" t="n">
-        <v>5.5533</v>
+        <v>-0.6226</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3002</v>
+        <v>-0.0364</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2531</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.7854</v>
+        <v>-1.9493</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.1317</v>
+        <v>-1.6694</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6537</v>
+        <v>-0.2799</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.386</v>
+        <v>0.386</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5091</v>
+        <v>1.3511</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9069</v>
+        <v>0.7301</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1303</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7766999999999999</v>
+        <v>0.0159</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1228</v>
+        <v>-0.6562</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3281</v>
+        <v>-0.3704</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2053</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. ELOSEGUI OLANO</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1154</v>
+        <v>-2.1901</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0426</v>
+        <v>-1.1401</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0727</v>
+        <v>-1.0501</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1265</v>
+        <v>-2.7323</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4461</v>
+        <v>-3.457</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6805</v>
+        <v>0.7247</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0414</v>
+        <v>0.1978</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0414</v>
+        <v>-1.2267</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.4245</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1679</v>
+        <v>-2.93</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4875</v>
+        <v>-2.2303</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6805</v>
+        <v>-0.6998</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>0.193</v>
+        <v>2.1231</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2168</v>
+        <v>0.1861</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.119</v>
+        <v>0.0205</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0978</v>
+        <v>0.1656</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1631</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.4087</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4172</v>
+        <v>-2.6125</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9678</v>
+        <v>-0.7081</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4493</v>
+        <v>-1.9044</v>
       </c>
       <c r="G11" t="n">
         <v>-3.5436</v>
@@ -1312,13 +1312,13 @@
         <v>2.3161</v>
       </c>
       <c r="S11" t="n">
-        <v>0.47</v>
+        <v>0.2746</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4032</v>
+        <v>-0.1434</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8731</v>
+        <v>0.418</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6945</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.769</v>
+        <v>-6.6804</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2727</v>
+        <v>-3.3714</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.4964</v>
+        <v>-3.309</v>
       </c>
       <c r="G12" t="n">
         <v>-6.8613</v>
@@ -1390,13 +1390,13 @@
         <v>2.1231</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6571</v>
+        <v>-0.5684</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0113</v>
+        <v>-0.11</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6458</v>
+        <v>-0.4584</v>
       </c>
       <c r="V12" t="n">
         <v>-0.4087</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.7992</v>
+        <v>-13.5018</v>
       </c>
       <c r="E13" t="n">
-        <v>3.559299999999999</v>
+        <v>3.8567</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.3584</v>
+        <v>-17.3586</v>
       </c>
       <c r="G13" t="n">
         <v>-22.3286</v>
@@ -1441,7 +1441,7 @@
         <v>-6.1051</v>
       </c>
       <c r="J13" t="n">
-        <v>7.872399999999999</v>
+        <v>7.872400000000001</v>
       </c>
       <c r="K13" t="n">
         <v>3.641900000000001</v>
@@ -1468,13 +1468,13 @@
         <v>17.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7467000000000005</v>
+        <v>-0.4494</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.01969999999999983</v>
+        <v>0.2778999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7273000000000001</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.5562</v>
@@ -1483,7 +1483,7 @@
         <v>5.3568</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.801</v>
+        <v>-3.801000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.543</v>
+        <v>7.2112</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5901</v>
+        <v>6.9907</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0471</v>
+        <v>0.2206</v>
       </c>
       <c r="G14" t="n">
         <v>6.1756</v>
@@ -1546,13 +1546,13 @@
         <v>0.965</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8606</v>
+        <v>-0.1924</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5354</v>
+        <v>-0.1348</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3252</v>
+        <v>-0.0575</v>
       </c>
       <c r="V14" t="n">
         <v>1.228</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>I. CHACON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0567</v>
+        <v>1.961</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9863</v>
+        <v>1.12</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0704</v>
+        <v>0.841</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0516</v>
+        <v>1.0577</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1052</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0536</v>
+        <v>0.1499</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9934</v>
+        <v>0.9908</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0737</v>
+        <v>0.828</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9197</v>
+        <v>0.1628</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9418</v>
+        <v>0.067</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9685</v>
+        <v>0.0798</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9732</v>
+        <v>-0.0129</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.965</v>
+        <v>0.772</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2157</v>
+        <v>-0.1547</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5792</v>
+        <v>-0.1566</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6365</v>
+        <v>0.002</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2456</v>
+        <v>0.2859</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6562</v>
+        <v>0.2859</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. BETOLAZA BELOKI</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0261</v>
+        <v>1.8992</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6089</v>
+        <v>2.2839</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5829</v>
+        <v>-0.3847</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1652</v>
+        <v>2.0516</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7297</v>
+        <v>2.1052</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4355</v>
+        <v>-0.0536</v>
       </c>
       <c r="J16" t="n">
-        <v>4.0527</v>
+        <v>3.9934</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4644</v>
+        <v>3.0737</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5883</v>
+        <v>0.9197</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8875</v>
+        <v>-1.9418</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7347</v>
+        <v>-0.9685</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1528</v>
+        <v>-0.9732</v>
       </c>
       <c r="P16" t="n">
         <v>-0.965</v>
@@ -1702,28 +1702,28 @@
         <v>0.965</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6854</v>
+        <v>1.0582</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8144</v>
+        <v>0.8768</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1289</v>
+        <v>0.1814</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8596</v>
+        <v>-0.2456</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3281</v>
+        <v>-0.6562</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5315</v>
+        <v>0.4106</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. CHACON RODRIGUEZ</t>
+          <t>E. SALINERO GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8142</v>
+        <v>1.6045</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9197</v>
+        <v>2.6583</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8945</v>
+        <v>-1.0539</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0577</v>
+        <v>4.7001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9078000000000001</v>
+        <v>1.4034</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1499</v>
+        <v>3.2966</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9908</v>
+        <v>5.2471</v>
       </c>
       <c r="K17" t="n">
-        <v>0.828</v>
+        <v>2.0647</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1628</v>
+        <v>3.1824</v>
       </c>
       <c r="M17" t="n">
-        <v>0.067</v>
+        <v>-0.547</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0798</v>
+        <v>-0.6612</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0129</v>
+        <v>0.1142</v>
       </c>
       <c r="P17" t="n">
-        <v>0.772</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R17" t="n">
         <v>0.772</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3014</v>
+        <v>0.2152</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3569</v>
+        <v>0.0205</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0555</v>
+        <v>0.1946</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2859</v>
+        <v>-1.1877</v>
       </c>
       <c r="W17" t="n">
         <v>0.2859</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.4736</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. NDIAYE SOW</t>
+          <t>I. BETOLAZA BELOKI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6784</v>
+        <v>1.5521</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3765</v>
+        <v>2.1082</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3019</v>
+        <v>-0.5561</v>
       </c>
       <c r="G18" t="n">
-        <v>2.683</v>
+        <v>3.1652</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8641</v>
+        <v>0.7297</v>
       </c>
       <c r="I18" t="n">
-        <v>0.819</v>
+        <v>2.4355</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3892</v>
+        <v>4.0527</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6973</v>
+        <v>1.4644</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6919</v>
+        <v>2.5883</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2938</v>
+        <v>-0.8875</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1667</v>
+        <v>-0.7347</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1271</v>
+        <v>-0.1528</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.7371</v>
+        <v>-0.965</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>1.158</v>
+        <v>0.965</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9604</v>
+        <v>0.2115</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3107</v>
+        <v>0.3137</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6497000000000001</v>
+        <v>-0.1021</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.228</v>
+        <v>-0.8596</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5717</v>
+        <v>-0.3281</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7997</v>
+        <v>-0.5315</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. SALINERO GARCIA</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6021</v>
+        <v>1.0563</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0575</v>
+        <v>2.0333</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4554</v>
+        <v>-0.9771</v>
       </c>
       <c r="G19" t="n">
-        <v>4.7001</v>
+        <v>-0.1027</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4034</v>
+        <v>0.2536</v>
       </c>
       <c r="I19" t="n">
-        <v>3.2966</v>
+        <v>-0.3563</v>
       </c>
       <c r="J19" t="n">
-        <v>5.2471</v>
+        <v>1.3988</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0647</v>
+        <v>1.1953</v>
       </c>
       <c r="L19" t="n">
-        <v>3.1824</v>
+        <v>0.2035</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.547</v>
+        <v>-1.5015</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6612</v>
+        <v>-0.9417</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1142</v>
+        <v>-0.5598</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.1231</v>
+        <v>1.158</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.772</v>
+        <v>1.158</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7872</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5803</v>
+        <v>0.0205</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2069</v>
+        <v>-0.1021</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1877</v>
+        <v>0.0825</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2859</v>
+        <v>0.614</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4736</v>
+        <v>-0.5315</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>B. MENDIA SANGRONIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4286</v>
+        <v>0.6355</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4325</v>
+        <v>1.086</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0038</v>
+        <v>-0.4504</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1027</v>
+        <v>1.5908</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2536</v>
+        <v>3.7042</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3563</v>
+        <v>-2.1135</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3988</v>
+        <v>2.3512</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1953</v>
+        <v>3.6378</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2035</v>
+        <v>-1.2866</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5015</v>
+        <v>-0.7604</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9417</v>
+        <v>0.0664</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5598</v>
+        <v>-0.8268</v>
       </c>
       <c r="P20" t="n">
-        <v>1.158</v>
+        <v>-0.965</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>1.158</v>
+        <v>0.965</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.6042</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5803</v>
+        <v>-0.235</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1289</v>
+        <v>-0.3692</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0825</v>
+        <v>0.614</v>
       </c>
       <c r="W20" t="n">
-        <v>0.614</v>
+        <v>0.8999</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5315</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3651</v>
+        <v>0.3918</v>
       </c>
       <c r="E21" t="n">
         <v>0.0207</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3444</v>
+        <v>0.3711</v>
       </c>
       <c r="G21" t="n">
         <v>0.1542</v>
@@ -2092,13 +2092,13 @@
         <v>0.193</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. MENDIA SANGRONIZ</t>
+          <t>M. ERRASTI UGARTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.09420000000000001</v>
+        <v>-0.129</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7856</v>
+        <v>-0.2932</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6914</v>
+        <v>0.1642</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5908</v>
+        <v>0.7319</v>
       </c>
       <c r="H22" t="n">
-        <v>3.7042</v>
+        <v>-0.0528</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1135</v>
+        <v>0.7847</v>
       </c>
       <c r="J22" t="n">
-        <v>2.3512</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6378</v>
+        <v>0.0207</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2866</v>
+        <v>0.6512</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7604</v>
+        <v>0.06</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0664</v>
+        <v>-0.0735</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8268</v>
+        <v>0.1335</v>
       </c>
       <c r="P22" t="n">
+        <v>-0.772</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-0.965</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-1.9301</v>
-      </c>
       <c r="R22" t="n">
-        <v>0.965</v>
+        <v>0.193</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1455</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5354</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6101</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8999</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. ERRASTI UGARTE</t>
+          <t>M. NDIAYE SOW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1558</v>
+        <v>-0.1772</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2932</v>
+        <v>-0.0241</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1374</v>
+        <v>-0.1532</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7319</v>
+        <v>2.683</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0528</v>
+        <v>1.8641</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7847</v>
+        <v>0.819</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6719000000000001</v>
+        <v>2.3892</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0207</v>
+        <v>1.6973</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6512</v>
+        <v>0.6919</v>
       </c>
       <c r="M23" t="n">
-        <v>0.06</v>
+        <v>0.2938</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0735</v>
+        <v>0.1667</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1335</v>
+        <v>0.1271</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.772</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R23" t="n">
-        <v>0.193</v>
+        <v>1.158</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1157</v>
+        <v>0.1048</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1157</v>
+        <v>0.1946</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7984</v>
+        <v>-0.3047</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7376</v>
+        <v>-0.1368</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0608</v>
+        <v>-0.1679</v>
       </c>
       <c r="G24" t="n">
         <v>0.8449</v>
@@ -2326,13 +2326,13 @@
         <v>0.579</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0185</v>
+        <v>0.5123</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4614</v>
+        <v>0.1395</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4799</v>
+        <v>0.3728</v>
       </c>
       <c r="V24" t="n">
         <v>0.6543</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.855</v>
+        <v>-1.9016</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3886</v>
+        <v>-0.4888</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4664</v>
+        <v>-1.4128</v>
       </c>
       <c r="G25" t="n">
         <v>-0.7238</v>
@@ -2404,13 +2404,13 @@
         <v>0.965</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2313</v>
+        <v>-0.278</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0727</v>
+        <v>-0.0274</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3041</v>
+        <v>-0.2505</v>
       </c>
       <c r="V25" t="n">
         <v>-0.8999</v>
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>13.7992</v>
+        <v>13.7991</v>
       </c>
       <c r="E26" t="n">
-        <v>17.3584</v>
+        <v>17.3582</v>
       </c>
       <c r="F26" t="n">
         <v>-3.5592</v>
@@ -2452,7 +2452,7 @@
         <v>16.2237</v>
       </c>
       <c r="I26" t="n">
-        <v>6.104700000000001</v>
+        <v>6.1047</v>
       </c>
       <c r="J26" t="n">
         <v>30.2011</v>
@@ -2464,7 +2464,7 @@
         <v>10.3356</v>
       </c>
       <c r="M26" t="n">
-        <v>-7.8725</v>
+        <v>-7.872500000000001</v>
       </c>
       <c r="N26" t="n">
         <v>-3.6417</v>
@@ -2482,13 +2482,13 @@
         <v>9.65</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7469000000000003</v>
+        <v>0.7468000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>0.7273000000000001</v>
+        <v>0.7273000000000002</v>
       </c>
       <c r="U26" t="n">
-        <v>0.01960000000000012</v>
+        <v>0.01970000000000011</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5561</v>
@@ -2497,7 +2497,7 @@
         <v>3.801</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.357099999999999</v>
+        <v>-5.3571</v>
       </c>
     </row>
   </sheetData>
